--- a/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 14,26</t>
+          <t>0,23; 14,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 3,02</t>
+          <t>-13,7; 3,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 9,34</t>
+          <t>-6,17; 9,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 2,31</t>
+          <t>-17,95; 2,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 350,71</t>
+          <t>-4,87; 415,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 27,32</t>
+          <t>-63,0; 35,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 262,03</t>
+          <t>-60,87; 213,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,67; 38,97</t>
+          <t>-84,13; 43,18</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 5,24</t>
+          <t>-1,61; 5,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 4,37</t>
+          <t>-2,28; 4,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,93</t>
+          <t>-3,26; 3,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,84</t>
+          <t>-4,26; 2,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 68,3</t>
+          <t>-14,71; 63,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 50,44</t>
+          <t>-18,86; 55,14</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-30,52; 36,52</t>
+          <t>-29,28; 38,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 34,76</t>
+          <t>-35,98; 33,6</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 6,51</t>
+          <t>-3,86; 6,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,95</t>
+          <t>-7,78; 2,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 5,57</t>
+          <t>-4,7; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 1,91</t>
+          <t>-9,26; 1,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 90,82</t>
+          <t>-33,1; 97,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,5; 27,57</t>
+          <t>-59,83; 40,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 89,01</t>
+          <t>-42,29; 93,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-59,76; 22,45</t>
+          <t>-61,44; 25,2</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 4,69</t>
+          <t>-0,71; 4,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,08</t>
+          <t>-3,19; 2,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 2,38</t>
+          <t>-2,4; 2,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 0,89</t>
+          <t>-4,76; 0,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 57,0</t>
+          <t>-6,85; 58,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 21,22</t>
+          <t>-26,64; 22,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,05; 29,0</t>
+          <t>-23,71; 31,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,4; 9,3</t>
+          <t>-38,27; 9,81</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según que han tenido una quemadura en el último año</t>
+          <t>Menores según si han tenido una quemadura solar, con o sin ampollas, en el último año</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 14,02</t>
+          <t>-0,05; 14,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 3,85</t>
+          <t>-13,62; 3,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 9,24</t>
+          <t>-6,54; 9,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,95; 2,66</t>
+          <t>-16,42; 2,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 415,53</t>
+          <t>-4,09; 406,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,0; 35,54</t>
+          <t>-63,85; 32,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 213,71</t>
+          <t>-61,2; 290,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-84,13; 43,18</t>
+          <t>-82,08; 45,71</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,13</t>
+          <t>-1,49; 5,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,55</t>
+          <t>-2,1; 4,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 3,1</t>
+          <t>-3,54; 2,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 2,73</t>
+          <t>-4,47; 2,96</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-14,71; 63,38</t>
+          <t>-13,52; 59,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,86; 55,14</t>
+          <t>-18,44; 52,15</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 38,1</t>
+          <t>-31,23; 33,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 33,6</t>
+          <t>-36,68; 35,95</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 6,71</t>
+          <t>-4,42; 6,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 2,56</t>
+          <t>-8,13; 2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 5,55</t>
+          <t>-4,63; 5,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 1,54</t>
+          <t>-9,22; 1,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,1; 97,14</t>
+          <t>-36,77; 86,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,83; 40,26</t>
+          <t>-62,33; 34,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 93,54</t>
+          <t>-40,49; 87,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,44; 25,2</t>
+          <t>-61,76; 21,25</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 4,69</t>
+          <t>-0,34; 4,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 2,12</t>
+          <t>-3,18; 2,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,56</t>
+          <t>-2,4; 2,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 0,84</t>
+          <t>-4,77; 1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 58,57</t>
+          <t>-3,34; 57,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-26,64; 22,81</t>
+          <t>-25,56; 22,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,71; 31,76</t>
+          <t>-23,06; 35,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,27; 9,81</t>
+          <t>-39,1; 11,24</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-6,62</t>
+          <t>-6,38</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-46,69%</t>
+          <t>-40,75%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 14,16</t>
+          <t>-0,66; 14,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,62; 3,48</t>
+          <t>-13,8; 3,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 9,89</t>
+          <t>-6,95; 9,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 2,78</t>
+          <t>-20,15; 3,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 406,67</t>
+          <t>-14,98; 350,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-63,85; 32,21</t>
+          <t>-62,56; 27,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-61,2; 290,59</t>
+          <t>-63,56; 262,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 45,71</t>
+          <t>-81,61; 47,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-7,15%</t>
+          <t>-3,67%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 5,05</t>
+          <t>-1,2; 5,24</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,36</t>
+          <t>-2,2; 4,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,72</t>
+          <t>-3,4; 2,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,96</t>
+          <t>-3,83; 3,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-13,52; 59,91</t>
+          <t>-10,54; 68,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 52,15</t>
+          <t>-19,9; 50,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 33,71</t>
+          <t>-30,52; 36,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 35,95</t>
+          <t>-31,77; 41,94</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,51</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-29,79%</t>
+          <t>-28,63%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 6,61</t>
+          <t>-4,86; 6,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 2,49</t>
+          <t>-8,1; 1,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 5,89</t>
+          <t>-4,41; 5,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,79</t>
+          <t>-9,02; 2,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 86,28</t>
+          <t>-36,9; 90,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,33; 34,7</t>
+          <t>-64,5; 27,57</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-40,49; 87,6</t>
+          <t>-39,1; 89,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 21,25</t>
+          <t>-58,46; 29,44</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,86</t>
+          <t>-1,6</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-17,12%</t>
+          <t>-14,2%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 4,8</t>
+          <t>-0,43; 4,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,12</t>
+          <t>-3,27; 2,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 2,81</t>
+          <t>-2,42; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,0</t>
+          <t>-4,85; 1,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 57,16</t>
+          <t>-4,29; 57,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,56; 22,62</t>
+          <t>-26,38; 21,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,06; 35,39</t>
+          <t>-23,05; 29,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 11,24</t>
+          <t>-37,23; 12,17</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP26C_R-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>6,75</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,92</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-6,38</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,3%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-29,25%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-40,75%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>6.749145503036055</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.923172364481348</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.296386076684819</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-6.3770401630378</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.00302338200392</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.2925173271885642</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.1757896991045443</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.4074677728720854</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-0,66; 14,26</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-13,8; 3,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,95; 9,34</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-20,15; 3,56</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-14,98; 350,71</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-62,56; 27,32</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-63,56; 262,03</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-81,61; 47,42</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-0.6627753086119924</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-13.79922980026355</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.949720859802292</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-20.15447143018253</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.1497632964142232</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6256209468551938</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6356070625165225</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.8160726363885423</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>14.26096326658944</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.024538930472825</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.341993068111917</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>3.560621216836806</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.507090645505031</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2731983864007771</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2.62029929993652</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.474225519984519</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,72</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>1,08</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,18</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-3,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,2; 5,24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 4,37</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-3,4; 2,93</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,83; 3,5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-10,54; 68,3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-19,9; 50,44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-30,52; 36,52</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-31,77; 41,94</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.721397111433008</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.081495837005508</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1844108527474742</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.3853721720110254</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.176625125483522</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.1064089265884491</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.01910151436759518</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.03673115112564076</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,99</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-2,84</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-3,46</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,87%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-28,11%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-28,63%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.199663270140498</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-2.204118627286114</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-3.395348995193858</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.829730270352616</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1054300280123552</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1989895326076453</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3051846098217963</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3176717647963697</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,86; 6,51</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,1; 1,95</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 5,57</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,02; 2,02</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-36,9; 90,82</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-64,5; 27,57</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-39,1; 89,01</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-58,46; 29,44</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.238300279393612</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.368407485525577</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.926649222079101</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.500977807764737</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.6829992754871973</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.5043686729094653</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.3652381176032188</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4193687147660211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,18</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,11</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,7%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-14,2%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.9893945806800377</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-2.838453895356223</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.4040636976137116</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-3.462609046099552</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.09871574853310566</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2811264603511842</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.04454149815670948</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.2863222827922263</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-0,43; 4,69</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,27; 2,08</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 2,38</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-4,85; 1,19</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-4,29; 57,0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-26,38; 21,22</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-23,05; 29,0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-37,23; 12,17</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.864545328853727</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.100375613610963</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.413868446521091</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-9.021925263612648</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3689668944133872</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.6450467308592434</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.3910290527571481</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.5846286802736326</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>6.506922031746175</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.946543758536887</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.567544500526614</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.023896113228643</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.9082184348171035</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2757491916942708</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.8901059808368993</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.2944077422621396</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>2.177115958497146</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.5137183499775253</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1082508893619716</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.603272244924081</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.2305398713042435</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.04704260938971508</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.01164537794615412</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1419501103175623</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.4304714427084446</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.274296759245702</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.422760957011231</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-4.850899597230437</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.04291166866967971</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2637929010530216</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.2304963226366993</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.37226609687794</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.686602941894172</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.077010009386342</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.376382194216286</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.186454111769304</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5699874043710524</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2122444505328331</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2899793846663513</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1217311789066813</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
